--- a/davomat.xlsx
+++ b/davomat.xlsx
@@ -5,13 +5,17 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="15-07-2026" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="16-07-2026" state="visible" r:id="rId5"/>
+    <sheet sheetId="5" name="17-07-2026" state="visible" r:id="rId6"/>
+    <sheet sheetId="3" name="Oylik 07-2026" state="visible" r:id="rId7"/>
+    <sheet sheetId="4" name="Yillik 2026" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="21">
   <si>
     <t>Ishchi ismi</t>
   </si>
@@ -47,6 +51,33 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>shoxi</t>
+  </si>
+  <si>
+    <t>Keldi</t>
+  </si>
+  <si>
+    <t>06:51:21</t>
+  </si>
+  <si>
+    <t>Kelgan kunlar</t>
+  </si>
+  <si>
+    <t>Kech qolgan kunlar</t>
+  </si>
+  <si>
+    <t>Jami kech qolish (daqiqa)</t>
+  </si>
+  <si>
+    <t>Jami jarima (so'm)</t>
+  </si>
+  <si>
+    <t>Jami ishlagan soat</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
 </sst>
 </file>
@@ -69,7 +100,7 @@
       <color rgb="FF9A3412"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -79,6 +110,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,10 +130,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -498,6 +535,256 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
 </file>
--- a/davomat.xlsx
+++ b/davomat.xlsx
@@ -4,18 +4,16 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="15-07-2026" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="16-07-2026" state="visible" r:id="rId5"/>
-    <sheet sheetId="5" name="17-07-2026" state="visible" r:id="rId6"/>
-    <sheet sheetId="3" name="Oylik 07-2026" state="visible" r:id="rId7"/>
-    <sheet sheetId="4" name="Yillik 2026" state="visible" r:id="rId8"/>
+    <sheet sheetId="1" name="18-07-2026" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Oylik 07-2026" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Yillik 2026" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
   <si>
     <t>Ishchi ismi</t>
   </si>
@@ -53,15 +51,6 @@
     <t/>
   </si>
   <si>
-    <t>shoxi</t>
-  </si>
-  <si>
-    <t>Keldi</t>
-  </si>
-  <si>
-    <t>06:51:21</t>
-  </si>
-  <si>
     <t>Kelgan kunlar</t>
   </si>
   <si>
@@ -75,9 +64,6 @@
   </si>
   <si>
     <t>Jami ishlagan soat</t>
-  </si>
-  <si>
-    <t>0.00</t>
   </si>
 </sst>
 </file>
@@ -541,74 +527,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -623,39 +542,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -664,9 +563,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -681,110 +580,23 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
 </file>